--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,45 +1206,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104320464</v>
+        <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87358</v>
+        <v>87365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3727</v>
+        <v>3712</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Klenodspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius spectabilis</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute stora valle, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>736339</v>
+        <v>736449</v>
       </c>
       <c r="R7" t="n">
-        <v>6411426</v>
+        <v>6411651</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1271,12 +1271,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1291,53 +1301,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104320464</t>
+          <t>https://artportalen.se/Sighting/137223033</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104320433</v>
+        <v>104320464</v>
       </c>
       <c r="B8" t="n">
-        <v>92869</v>
+        <v>87358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>3727</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Klenodspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius spectabilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>736362</v>
+        <v>736339</v>
       </c>
       <c r="R8" t="n">
-        <v>6411459</v>
+        <v>6411426</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,16 +1418,16 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104320433</t>
+          <t>https://artportalen.se/Sighting/104320464</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128203023</v>
+        <v>104320433</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1429,46 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
+          <t>Gotland, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>736365</v>
+        <v>736362</v>
       </c>
       <c r="R9" t="n">
-        <v>6411573</v>
+        <v>6411459</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1492,12 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2022-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2022-10-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,33 +1505,32 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Sten Svantesson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203023</t>
+          <t>https://artportalen.se/Sighting/104320433</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128205915</v>
+        <v>128203023</v>
       </c>
       <c r="B10" t="n">
         <v>57950</v>
@@ -1569,7 +1565,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1578,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>736315</v>
+        <v>736365</v>
       </c>
       <c r="R10" t="n">
-        <v>6411597</v>
+        <v>6411573</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1644,16 +1640,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128205915</t>
+          <t>https://artportalen.se/Sighting/128203023</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128203101</v>
+        <v>128205915</v>
       </c>
       <c r="B11" t="n">
-        <v>99026</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,31 +1657,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219788</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1694,13 +1690,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>736358</v>
+        <v>736315</v>
       </c>
       <c r="R11" t="n">
-        <v>6411725</v>
+        <v>6411597</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1743,7 +1739,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1760,13 +1756,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203101</t>
+          <t>https://artportalen.se/Sighting/128205915</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128203195</v>
+        <v>128203101</v>
       </c>
       <c r="B12" t="n">
         <v>99026</v>
@@ -1796,7 +1792,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1810,13 +1806,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>736314</v>
+        <v>736358</v>
       </c>
       <c r="R12" t="n">
-        <v>6411572</v>
+        <v>6411725</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1848,11 +1844,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1864,7 +1855,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr, kalkgräsmyr, agmyr i mosaik.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1881,16 +1872,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203195</t>
+          <t>https://artportalen.se/Sighting/128203101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128203081</v>
+        <v>128203195</v>
       </c>
       <c r="B13" t="n">
-        <v>99096</v>
+        <v>99026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,26 +1889,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>219788</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1931,13 +1922,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>736347</v>
+        <v>736314</v>
       </c>
       <c r="R13" t="n">
-        <v>6411466</v>
+        <v>6411572</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1969,6 +1960,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1980,7 +1976,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1997,13 +1993,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203081</t>
+          <t>https://artportalen.se/Sighting/128203195</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128203084</v>
+        <v>128203081</v>
       </c>
       <c r="B14" t="n">
         <v>99096</v>
@@ -2033,7 +2029,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2047,10 +2043,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>736442</v>
+        <v>736347</v>
       </c>
       <c r="R14" t="n">
-        <v>6411479</v>
+        <v>6411466</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,13 +2109,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203084</t>
+          <t>https://artportalen.se/Sighting/128203081</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128203086</v>
+        <v>128203084</v>
       </c>
       <c r="B15" t="n">
         <v>99096</v>
@@ -2149,7 +2145,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2163,10 +2159,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>736450</v>
+        <v>736442</v>
       </c>
       <c r="R15" t="n">
-        <v>6411486</v>
+        <v>6411479</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,13 +2225,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203086</t>
+          <t>https://artportalen.se/Sighting/128203084</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128203088</v>
+        <v>128203086</v>
       </c>
       <c r="B16" t="n">
         <v>99096</v>
@@ -2265,7 +2261,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2279,10 +2275,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>736474</v>
+        <v>736450</v>
       </c>
       <c r="R16" t="n">
-        <v>6411506</v>
+        <v>6411486</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2345,13 +2341,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203088</t>
+          <t>https://artportalen.se/Sighting/128203086</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128203089</v>
+        <v>128203088</v>
       </c>
       <c r="B17" t="n">
         <v>99096</v>
@@ -2381,7 +2377,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2395,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>736488</v>
+        <v>736474</v>
       </c>
       <c r="R17" t="n">
-        <v>6411510</v>
+        <v>6411506</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2461,13 +2457,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203089</t>
+          <t>https://artportalen.se/Sighting/128203088</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128203092</v>
+        <v>128203089</v>
       </c>
       <c r="B18" t="n">
         <v>99096</v>
@@ -2497,7 +2493,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2511,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>736520</v>
+        <v>736488</v>
       </c>
       <c r="R18" t="n">
-        <v>6411544</v>
+        <v>6411510</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2577,13 +2573,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203092</t>
+          <t>https://artportalen.se/Sighting/128203089</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128203094</v>
+        <v>128203092</v>
       </c>
       <c r="B19" t="n">
         <v>99096</v>
@@ -2627,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>736498</v>
+        <v>736520</v>
       </c>
       <c r="R19" t="n">
-        <v>6411566</v>
+        <v>6411544</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,13 +2689,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203094</t>
+          <t>https://artportalen.se/Sighting/128203092</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128203096</v>
+        <v>128203094</v>
       </c>
       <c r="B20" t="n">
         <v>99096</v>
@@ -2729,7 +2725,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2743,10 +2739,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>736474</v>
+        <v>736498</v>
       </c>
       <c r="R20" t="n">
-        <v>6411596</v>
+        <v>6411566</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2781,11 +2777,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2814,13 +2805,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203096</t>
+          <t>https://artportalen.se/Sighting/128203094</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128203100</v>
+        <v>128203096</v>
       </c>
       <c r="B21" t="n">
         <v>99096</v>
@@ -2850,7 +2841,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2864,10 +2855,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>736361</v>
+        <v>736474</v>
       </c>
       <c r="R21" t="n">
-        <v>6411697</v>
+        <v>6411596</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2902,6 +2893,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Avsnitslad mindre svacka utan fukt mot SO:</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2930,13 +2926,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203100</t>
+          <t>https://artportalen.se/Sighting/128203096</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128203182</v>
+        <v>128203100</v>
       </c>
       <c r="B22" t="n">
         <v>99096</v>
@@ -2966,7 +2962,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2980,13 +2976,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>736350</v>
+        <v>736361</v>
       </c>
       <c r="R22" t="n">
-        <v>6411491</v>
+        <v>6411697</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3016,11 +3012,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Stig över våtmark; avsnitslat.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,13 +3042,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203182</t>
+          <t>https://artportalen.se/Sighting/128203100</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128203187</v>
+        <v>128203182</v>
       </c>
       <c r="B23" t="n">
         <v>99096</v>
@@ -3087,7 +3078,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3101,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>736331</v>
+        <v>736350</v>
       </c>
       <c r="R23" t="n">
-        <v>6411530</v>
+        <v>6411491</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3139,6 +3130,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Stig över våtmark; avsnitslat.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3167,13 +3163,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203187</t>
+          <t>https://artportalen.se/Sighting/128203182</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128203190</v>
+        <v>128203187</v>
       </c>
       <c r="B24" t="n">
         <v>99096</v>
@@ -3203,7 +3199,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3217,10 +3213,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>736335</v>
+        <v>736331</v>
       </c>
       <c r="R24" t="n">
-        <v>6411533</v>
+        <v>6411530</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3283,13 +3279,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203190</t>
+          <t>https://artportalen.se/Sighting/128203187</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128203216</v>
+        <v>128203190</v>
       </c>
       <c r="B25" t="n">
         <v>99096</v>
@@ -3333,10 +3329,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>736297</v>
+        <v>736335</v>
       </c>
       <c r="R25" t="n">
-        <v>6411559</v>
+        <v>6411533</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3371,11 +3367,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Kant av våtmark.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3404,16 +3395,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203216</t>
+          <t>https://artportalen.se/Sighting/128203190</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128203177</v>
+        <v>128203216</v>
       </c>
       <c r="B26" t="n">
-        <v>99103</v>
+        <v>99096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3421,16 +3412,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219799</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3438,20 +3429,29 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>736300</v>
+        <v>736297</v>
       </c>
       <c r="R26" t="n">
-        <v>6411481</v>
+        <v>6411559</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Kant av våtmark.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3516,13 +3516,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203177</t>
+          <t>https://artportalen.se/Sighting/128203216</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128203199</v>
+        <v>128203177</v>
       </c>
       <c r="B27" t="n">
         <v>99103</v>
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>736314</v>
+        <v>736300</v>
       </c>
       <c r="R27" t="n">
-        <v>6411572</v>
+        <v>6411481</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rätt rikligt spridd.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3628,13 +3628,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203199</t>
+          <t>https://artportalen.se/Sighting/128203177</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128203215</v>
+        <v>128203199</v>
       </c>
       <c r="B28" t="n">
         <v>99103</v>
@@ -3662,29 +3662,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>736301</v>
+        <v>736314</v>
       </c>
       <c r="R28" t="n">
-        <v>6411564</v>
+        <v>6411572</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3714,6 +3705,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3744,16 +3740,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203215</t>
+          <t>https://artportalen.se/Sighting/128203199</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128203173</v>
+        <v>128203215</v>
       </c>
       <c r="B29" t="n">
-        <v>99120</v>
+        <v>99103</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3761,26 +3757,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3794,13 +3790,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>736300</v>
+        <v>736301</v>
       </c>
       <c r="R29" t="n">
-        <v>6411439</v>
+        <v>6411564</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,7 +3839,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3860,13 +3856,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203173</t>
+          <t>https://artportalen.se/Sighting/128203215</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128203197</v>
+        <v>128203173</v>
       </c>
       <c r="B30" t="n">
         <v>99120</v>
@@ -3894,20 +3890,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>736314</v>
+        <v>736300</v>
       </c>
       <c r="R30" t="n">
-        <v>6411572</v>
+        <v>6411439</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3939,11 +3944,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3972,13 +3972,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203197</t>
+          <t>https://artportalen.se/Sighting/128203173</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128203207</v>
+        <v>128203197</v>
       </c>
       <c r="B31" t="n">
         <v>99120</v>
@@ -4006,29 +4006,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>736300</v>
+        <v>736314</v>
       </c>
       <c r="R31" t="n">
-        <v>6411576</v>
+        <v>6411572</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4058,6 +4049,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4088,13 +4084,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203207</t>
+          <t>https://artportalen.se/Sighting/128203197</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128203209</v>
+        <v>128203207</v>
       </c>
       <c r="B32" t="n">
         <v>99120</v>
@@ -4124,7 +4120,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4138,13 +4134,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>736295</v>
+        <v>736300</v>
       </c>
       <c r="R32" t="n">
-        <v>6411567</v>
+        <v>6411576</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4204,13 +4200,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203209</t>
+          <t>https://artportalen.se/Sighting/128203207</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128203213</v>
+        <v>128203209</v>
       </c>
       <c r="B33" t="n">
         <v>99120</v>
@@ -4254,10 +4250,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>736301</v>
+        <v>736295</v>
       </c>
       <c r="R33" t="n">
-        <v>6411564</v>
+        <v>6411567</v>
       </c>
       <c r="S33" t="n">
         <v>7</v>
@@ -4320,16 +4316,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203213</t>
+          <t>https://artportalen.se/Sighting/128203209</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128203186</v>
+        <v>128203213</v>
       </c>
       <c r="B34" t="n">
-        <v>99141</v>
+        <v>99120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4337,26 +4333,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219862</v>
+        <v>219811</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4370,13 +4366,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>736331</v>
+        <v>736301</v>
       </c>
       <c r="R34" t="n">
-        <v>6411530</v>
+        <v>6411564</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4419,7 +4415,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4436,54 +4432,63 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203186</t>
+          <t>https://artportalen.se/Sighting/128203213</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128203080</v>
+        <v>128203186</v>
       </c>
       <c r="B35" t="n">
-        <v>110078</v>
+        <v>99141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220299</v>
+        <v>219862</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>736347</v>
+        <v>736331</v>
       </c>
       <c r="R35" t="n">
-        <v>6411466</v>
+        <v>6411530</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4543,13 +4548,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203080</t>
+          <t>https://artportalen.se/Sighting/128203186</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128203082</v>
+        <v>128203080</v>
       </c>
       <c r="B36" t="n">
         <v>110078</v>
@@ -4584,10 +4589,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>736416</v>
+        <v>736347</v>
       </c>
       <c r="R36" t="n">
-        <v>6411452</v>
+        <v>6411466</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,11 +4627,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stig (avsnitslad) ut ur Stora Valle och in i Alvans 1:13 (2).</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4655,13 +4655,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203082</t>
+          <t>https://artportalen.se/Sighting/128203080</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128203083</v>
+        <v>128203082</v>
       </c>
       <c r="B37" t="n">
         <v>110078</v>
@@ -4696,10 +4696,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>736442</v>
+        <v>736416</v>
       </c>
       <c r="R37" t="n">
-        <v>6411479</v>
+        <v>6411452</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,6 +4734,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Stig (avsnitslad) ut ur Stora Valle och in i Alvans 1:13 (2).</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4762,13 +4767,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203083</t>
+          <t>https://artportalen.se/Sighting/128203082</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128203085</v>
+        <v>128203083</v>
       </c>
       <c r="B38" t="n">
         <v>110078</v>
@@ -4803,10 +4808,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>736450</v>
+        <v>736442</v>
       </c>
       <c r="R38" t="n">
-        <v>6411486</v>
+        <v>6411479</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4869,13 +4874,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203085</t>
+          <t>https://artportalen.se/Sighting/128203083</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128203087</v>
+        <v>128203085</v>
       </c>
       <c r="B39" t="n">
         <v>110078</v>
@@ -4910,10 +4915,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>736474</v>
+        <v>736450</v>
       </c>
       <c r="R39" t="n">
-        <v>6411506</v>
+        <v>6411486</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4976,13 +4981,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203087</t>
+          <t>https://artportalen.se/Sighting/128203085</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128203091</v>
+        <v>128203087</v>
       </c>
       <c r="B40" t="n">
         <v>110078</v>
@@ -5017,10 +5022,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>736520</v>
+        <v>736474</v>
       </c>
       <c r="R40" t="n">
-        <v>6411544</v>
+        <v>6411506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5083,13 +5088,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203091</t>
+          <t>https://artportalen.se/Sighting/128203087</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128203093</v>
+        <v>128203091</v>
       </c>
       <c r="B41" t="n">
         <v>110078</v>
@@ -5124,10 +5129,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>736498</v>
+        <v>736520</v>
       </c>
       <c r="R41" t="n">
-        <v>6411566</v>
+        <v>6411544</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5190,13 +5195,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203093</t>
+          <t>https://artportalen.se/Sighting/128203091</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128203095</v>
+        <v>128203093</v>
       </c>
       <c r="B42" t="n">
         <v>110078</v>
@@ -5231,10 +5236,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>736474</v>
+        <v>736498</v>
       </c>
       <c r="R42" t="n">
-        <v>6411596</v>
+        <v>6411566</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5269,11 +5274,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5302,13 +5302,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203095</t>
+          <t>https://artportalen.se/Sighting/128203093</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128203099</v>
+        <v>128203095</v>
       </c>
       <c r="B43" t="n">
         <v>110078</v>
@@ -5336,26 +5336,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>736361</v>
+        <v>736474</v>
       </c>
       <c r="R43" t="n">
-        <v>6411697</v>
+        <v>6411596</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5390,6 +5381,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Agmyr mot SV; avsnitslad naturhänsyn.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5418,13 +5414,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203099</t>
+          <t>https://artportalen.se/Sighting/128203095</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128203181</v>
+        <v>128203099</v>
       </c>
       <c r="B44" t="n">
         <v>110078</v>
@@ -5452,20 +5448,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>736350</v>
+        <v>736361</v>
       </c>
       <c r="R44" t="n">
-        <v>6411491</v>
+        <v>6411697</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5495,11 +5500,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-29</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5530,13 +5530,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203181</t>
+          <t>https://artportalen.se/Sighting/128203099</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128203185</v>
+        <v>128203181</v>
       </c>
       <c r="B45" t="n">
         <v>110078</v>
@@ -5571,10 +5571,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>736331</v>
+        <v>736350</v>
       </c>
       <c r="R45" t="n">
-        <v>6411530</v>
+        <v>6411491</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5642,13 +5642,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203185</t>
+          <t>https://artportalen.se/Sighting/128203181</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128203189</v>
+        <v>128203185</v>
       </c>
       <c r="B46" t="n">
         <v>110078</v>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>736335</v>
+        <v>736331</v>
       </c>
       <c r="R46" t="n">
-        <v>6411533</v>
+        <v>6411530</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5721,6 +5721,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5749,13 +5754,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203189</t>
+          <t>https://artportalen.se/Sighting/128203185</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128203220</v>
+        <v>128203189</v>
       </c>
       <c r="B47" t="n">
         <v>110078</v>
@@ -5783,26 +5788,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>736295</v>
+        <v>736335</v>
       </c>
       <c r="R47" t="n">
-        <v>6411551</v>
+        <v>6411533</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5837,11 +5833,6 @@
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5870,16 +5861,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203220</t>
+          <t>https://artportalen.se/Sighting/128203189</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128203180</v>
+        <v>128203220</v>
       </c>
       <c r="B48" t="n">
-        <v>106140</v>
+        <v>110078</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5887,16 +5878,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221137</v>
+        <v>220299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5904,20 +5895,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>736300</v>
+        <v>736295</v>
       </c>
       <c r="R48" t="n">
-        <v>6411481</v>
+        <v>6411551</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Naturhänsyn för våtmarken avsnitslad.</t>
+          <t>Även rikligt spridd. Strandvall mellan våtmarker.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkbarrskog över strandvallssystem med mellanligande svackor.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -5982,13 +5982,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203180</t>
+          <t>https://artportalen.se/Sighting/128203220</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128203192</v>
+        <v>128203180</v>
       </c>
       <c r="B49" t="n">
         <v>106140</v>
@@ -6016,29 +6016,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>736339</v>
+        <v>736300</v>
       </c>
       <c r="R49" t="n">
-        <v>6411571</v>
+        <v>6411481</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6086,7 +6077,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6103,54 +6094,63 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203192</t>
+          <t>https://artportalen.se/Sighting/128203180</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128203178</v>
+        <v>128203192</v>
       </c>
       <c r="B50" t="n">
-        <v>98642</v>
+        <v>106140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221930</v>
+        <v>221137</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kärrlilja</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tofieldia calyculata</t>
+          <t>Primula farinosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Wahlenb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>736300</v>
+        <v>736339</v>
       </c>
       <c r="R50" t="n">
-        <v>6411481</v>
+        <v>6411571</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rätt rikligt spridd.</t>
+          <t>Naturhänsyn för våtmarken avsnitslad.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6215,38 +6215,38 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203178</t>
+          <t>https://artportalen.se/Sighting/128203192</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128203211</v>
+        <v>128203178</v>
       </c>
       <c r="B51" t="n">
-        <v>99803</v>
+        <v>98642</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222322</v>
+        <v>221930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Kärrlilja</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Tofieldia calyculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Wahlenb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6256,13 +6256,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>736301</v>
+        <v>736300</v>
       </c>
       <c r="R51" t="n">
-        <v>6411564</v>
+        <v>6411481</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6294,6 +6294,11 @@
           <t>2025-08-29</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rätt rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6305,7 +6310,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Källmyr.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6322,38 +6327,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203211</t>
+          <t>https://artportalen.se/Sighting/128203178</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128203179</v>
+        <v>128203211</v>
       </c>
       <c r="B52" t="n">
-        <v>100171</v>
+        <v>99803</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222662</v>
+        <v>222322</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Axag</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Schoenus ferrugineus</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6363,13 +6368,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>736300</v>
+        <v>736301</v>
       </c>
       <c r="R52" t="n">
-        <v>6411481</v>
+        <v>6411564</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6412,7 +6417,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>Källmyr.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6429,54 +6434,54 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128203179</t>
+          <t>https://artportalen.se/Sighting/128203211</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>104320411</v>
+        <v>128203179</v>
       </c>
       <c r="B53" t="n">
-        <v>87262</v>
+        <v>100171</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>248956</v>
+        <v>222662</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Axag</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Schoenus ferrugineus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle 1:11 (2) SV-del, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>736341</v>
+        <v>736300</v>
       </c>
       <c r="R53" t="n">
-        <v>6411703</v>
+        <v>6411481</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6500,12 +6505,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6516,32 +6521,33 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Källmyr.</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sten Svantesson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Elisabet Ottosson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Inventering av kalkbarrskog på Gotland 2022</t>
-        </is>
-      </c>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104320411</t>
+          <t>https://artportalen.se/Sighting/128203179</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>104320452</v>
+        <v>104320411</v>
       </c>
       <c r="B54" t="n">
         <v>87262</v>
@@ -6576,10 +6582,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>736340</v>
+        <v>736341</v>
       </c>
       <c r="R54" t="n">
-        <v>6411442</v>
+        <v>6411703</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6641,38 +6647,38 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104320452</t>
+          <t>https://artportalen.se/Sighting/104320411</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>104320431</v>
+        <v>104320452</v>
       </c>
       <c r="B55" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6682,10 +6688,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>736362</v>
+        <v>736340</v>
       </c>
       <c r="R55" t="n">
-        <v>6411459</v>
+        <v>6411442</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6747,54 +6753,54 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104320431</t>
+          <t>https://artportalen.se/Sighting/104320452</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>104320453</v>
+        <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87346</v>
+        <v>87457</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gotland, Gtl</t>
+          <t>Rute Stora Valle, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>736340</v>
+        <v>736448</v>
       </c>
       <c r="R56" t="n">
-        <v>6411442</v>
+        <v>6411614</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6818,12 +6824,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-10-07</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-10-14</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6838,20 +6854,452 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137221656</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137221657</v>
+      </c>
+      <c r="B57" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>736440</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6411627</v>
+      </c>
+      <c r="S57" t="n">
+        <v>9</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137221657</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137221658</v>
+      </c>
+      <c r="B58" t="n">
+        <v>87457</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Rute Stora Valle, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>736437</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6411636</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137221658</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>104320431</v>
+      </c>
+      <c r="B59" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>736362</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6411459</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
           <t>Sten Svantesson</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
+      <c r="AX59" t="inlineStr">
         <is>
           <t>Sten Svantesson, Elisabet Ottosson</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr">
+      <c r="AY59" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104320431</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>104320453</v>
+      </c>
+      <c r="B60" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Gotland, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>736340</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6411442</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-10-14</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Sten Svantesson, Elisabet Ottosson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104320453</t>
         </is>
@@ -6914,6 +7362,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87365</v>
+        <v>87378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87457</v>
+        <v>87470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87378</v>
+        <v>87380</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87470</v>
+        <v>87472</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87380</v>
+        <v>87383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87383</v>
+        <v>87393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87397</v>
+        <v>87402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87402</v>
+        <v>87413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87413</v>
+        <v>87414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87414</v>
+        <v>87417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 61664-2023 artfynd.xlsx
+++ b/artfynd/A 61664-2023 artfynd.xlsx
@@ -1209,7 +1209,7 @@
         <v>137223033</v>
       </c>
       <c r="B7" t="n">
-        <v>87417</v>
+        <v>87421</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         <v>137221656</v>
       </c>
       <c r="B56" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>137221657</v>
       </c>
       <c r="B57" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>137221658</v>
       </c>
       <c r="B58" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
